--- a/docs/qa/stocktake-browser/stocktake-day1.xlsx
+++ b/docs/qa/stocktake-browser/stocktake-day1.xlsx
@@ -163,7 +163,7 @@
     <t>generatedAt</t>
   </si>
   <si>
-    <t>2026-08-02T14:22:51.046Z</t>
+    <t>2026-08-03T16:16:02.217Z</t>
   </si>
   <si>
     <t>generatedBy</t>
